--- a/results/greedy_params_choice_splashing_300iters_smote.xlsx
+++ b/results/greedy_params_choice_splashing_300iters_smote.xlsx
@@ -699,7 +699,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'K', 'sedimentation_Stk', 'inclination', 'wettability')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'particle_droplet_diameter_ratio', 'sedimentation_Stk', 'K', 'wettability', 'volume_fraction')</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'K', 'sedimentation_Stk', 'inclination', 'wettability')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'particle_droplet_diameter_ratio', 'sedimentation_Stk', 'K', 'wettability', 'volume_fraction')</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'relative_roughness', 'K', 'inclination', 'wettability')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'particle_droplet_diameter_ratio', 'K', 'wettability', 'volume_fraction', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'relative_roughness', 'K', 'inclination', 'wettability')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'particle_droplet_diameter_ratio', 'K', 'wettability', 'volume_fraction', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'relative_roughness', 'K', 'sedimentation_Stk', 'inclination', 'wettability')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'sedimentation_Stk', 'K', 'wettability', 'volume_fraction', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'relative_roughness', 'K', 'sedimentation_Stk', 'inclination', 'wettability')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'sedimentation_Stk', 'K', 'wettability', 'volume_fraction', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'relative_roughness', 'K', 'sedimentation_Stk', 'wettability')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'sedimentation_Stk', 'K', 'wettability', 'volume_fraction', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'relative_roughness', 'K', 'sedimentation_Stk', 'wettability')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'sedimentation_Stk', 'K', 'wettability', 'volume_fraction', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K', 'sedimentation_Stk', 'inclination', 'wettability')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'particle_droplet_diameter_ratio', 'sedimentation_Stk', 'K', 'wettability', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K', 'sedimentation_Stk', 'inclination', 'wettability')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'particle_droplet_diameter_ratio', 'sedimentation_Stk', 'K', 'wettability', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'relative_roughness', 'K', 'sedimentation_Stk', 'inclination')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'particle_droplet_diameter_ratio', 'sedimentation_Stk', 'K', 'volume_fraction', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'relative_roughness', 'K', 'sedimentation_Stk', 'inclination')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'particle_droplet_diameter_ratio', 'sedimentation_Stk', 'K', 'volume_fraction', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'relative_roughness', 'sedimentation_Stk', 'inclination', 'wettability')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'particle_droplet_diameter_ratio', 'sedimentation_Stk', 'wettability', 'volume_fraction', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'relative_roughness', 'sedimentation_Stk', 'inclination', 'wettability')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'particle_droplet_diameter_ratio', 'sedimentation_Stk', 'wettability', 'volume_fraction', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'K', 'inclination', 'wettability')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'particle_droplet_diameter_ratio', 'K', 'wettability', 'volume_fraction')</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'K', 'inclination', 'wettability')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'particle_droplet_diameter_ratio', 'K', 'wettability', 'volume_fraction')</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'K', 'sedimentation_Stk', 'inclination', 'wettability')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'sedimentation_Stk', 'K', 'wettability', 'volume_fraction')</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'K', 'sedimentation_Stk', 'inclination', 'wettability')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'sedimentation_Stk', 'K', 'wettability', 'volume_fraction')</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'K', 'sedimentation_Stk', 'wettability')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'sedimentation_Stk', 'K', 'wettability', 'volume_fraction')</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'K', 'sedimentation_Stk', 'wettability')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'sedimentation_Stk', 'K', 'wettability', 'volume_fraction')</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -4333,7 +4333,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'K', 'sedimentation_Stk', 'inclination', 'wettability')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'particle_droplet_diameter_ratio', 'sedimentation_Stk', 'K', 'wettability')</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'K', 'sedimentation_Stk', 'inclination', 'wettability')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'particle_droplet_diameter_ratio', 'sedimentation_Stk', 'K', 'wettability')</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'K', 'sedimentation_Stk', 'inclination')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'particle_droplet_diameter_ratio', 'sedimentation_Stk', 'K', 'volume_fraction')</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'K', 'sedimentation_Stk', 'inclination')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'particle_droplet_diameter_ratio', 'sedimentation_Stk', 'K', 'volume_fraction')</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -5061,7 +5061,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'sedimentation_Stk', 'inclination', 'wettability')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'particle_droplet_diameter_ratio', 'sedimentation_Stk', 'wettability', 'volume_fraction')</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'sedimentation_Stk', 'inclination', 'wettability')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'particle_droplet_diameter_ratio', 'sedimentation_Stk', 'wettability', 'volume_fraction')</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'relative_roughness', 'K', 'inclination', 'wettability')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'K', 'wettability', 'volume_fraction', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'relative_roughness', 'K', 'inclination', 'wettability')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'K', 'wettability', 'volume_fraction', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'relative_roughness', 'K', 'wettability')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'K', 'wettability', 'volume_fraction', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I30" t="n">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'relative_roughness', 'K', 'wettability')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'K', 'wettability', 'volume_fraction', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I31" t="n">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K', 'inclination', 'wettability')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'particle_droplet_diameter_ratio', 'K', 'wettability', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I32" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K', 'inclination', 'wettability')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'particle_droplet_diameter_ratio', 'K', 'wettability', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I33" t="n">
@@ -6517,7 +6517,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'relative_roughness', 'K', 'inclination')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'particle_droplet_diameter_ratio', 'K', 'volume_fraction', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I34" t="n">
@@ -6699,7 +6699,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'relative_roughness', 'K', 'inclination')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'particle_droplet_diameter_ratio', 'K', 'volume_fraction', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'relative_roughness', 'inclination', 'wettability')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'particle_droplet_diameter_ratio', 'wettability', 'volume_fraction', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I36" t="n">
@@ -7063,7 +7063,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'relative_roughness', 'inclination', 'wettability')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'particle_droplet_diameter_ratio', 'wettability', 'volume_fraction', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I37" t="n">
@@ -7245,7 +7245,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'relative_roughness', 'K', 'sedimentation_Stk', 'wettability')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'sedimentation_Stk', 'K', 'wettability', 'volume_fraction', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I38" t="n">
@@ -7427,7 +7427,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'relative_roughness', 'K', 'sedimentation_Stk', 'wettability')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'sedimentation_Stk', 'K', 'wettability', 'volume_fraction', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'relative_roughness', 'K', 'sedimentation_Stk', 'inclination', 'wettability')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'sedimentation_Stk', 'K', 'wettability', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I40" t="n">
@@ -7791,7 +7791,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'relative_roughness', 'K', 'sedimentation_Stk', 'inclination', 'wettability')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'sedimentation_Stk', 'K', 'wettability', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I41" t="n">
@@ -7973,7 +7973,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'relative_roughness', 'K', 'sedimentation_Stk', 'inclination')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'sedimentation_Stk', 'K', 'volume_fraction', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I42" t="n">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'relative_roughness', 'K', 'sedimentation_Stk', 'inclination')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'sedimentation_Stk', 'K', 'volume_fraction', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -8337,7 +8337,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'relative_roughness', 'sedimentation_Stk', 'inclination', 'wettability')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'sedimentation_Stk', 'wettability', 'volume_fraction', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I44" t="n">
@@ -8519,7 +8519,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'relative_roughness', 'sedimentation_Stk', 'inclination', 'wettability')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'sedimentation_Stk', 'wettability', 'volume_fraction', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I45" t="n">
@@ -8701,7 +8701,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K', 'sedimentation_Stk', 'wettability')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'sedimentation_Stk', 'K', 'wettability', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I46" t="n">
@@ -8883,7 +8883,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K', 'sedimentation_Stk', 'wettability')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'sedimentation_Stk', 'K', 'wettability', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I47" t="n">
@@ -9063,7 +9063,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'relative_roughness', 'K', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'sedimentation_Stk', 'K', 'volume_fraction', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I48" t="n">
@@ -9245,7 +9245,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'relative_roughness', 'K', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'sedimentation_Stk', 'K', 'volume_fraction', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I49" t="n">
@@ -9427,7 +9427,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'relative_roughness', 'sedimentation_Stk', 'wettability')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'sedimentation_Stk', 'wettability', 'volume_fraction', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I50" t="n">
@@ -9609,7 +9609,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'relative_roughness', 'sedimentation_Stk', 'wettability')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'sedimentation_Stk', 'wettability', 'volume_fraction', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I51" t="n">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K', 'sedimentation_Stk', 'inclination')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'particle_droplet_diameter_ratio', 'sedimentation_Stk', 'K', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I52" t="n">
@@ -9973,7 +9973,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K', 'sedimentation_Stk', 'inclination')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'particle_droplet_diameter_ratio', 'sedimentation_Stk', 'K', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I53" t="n">
@@ -10155,7 +10155,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'relative_roughness', 'sedimentation_Stk', 'inclination', 'wettability')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'particle_droplet_diameter_ratio', 'sedimentation_Stk', 'wettability', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I54" t="n">
@@ -10337,7 +10337,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'relative_roughness', 'sedimentation_Stk', 'inclination', 'wettability')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'particle_droplet_diameter_ratio', 'sedimentation_Stk', 'wettability', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I55" t="n">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'relative_roughness', 'sedimentation_Stk', 'inclination')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'particle_droplet_diameter_ratio', 'sedimentation_Stk', 'volume_fraction', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I56" t="n">
@@ -10701,7 +10701,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'relative_roughness', 'sedimentation_Stk', 'inclination')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'particle_droplet_diameter_ratio', 'sedimentation_Stk', 'volume_fraction', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I57" t="n">
@@ -10883,7 +10883,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'K', 'wettability', 'inclination')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'inclination', 'K', 'wettability')</t>
         </is>
       </c>
       <c r="I58" t="n">
@@ -11065,7 +11065,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'K', 'wettability', 'inclination')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'inclination', 'K', 'wettability')</t>
         </is>
       </c>
       <c r="I59" t="n">
@@ -11247,7 +11247,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'K', 'wettability')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'K', 'wettability', 'volume_fraction')</t>
         </is>
       </c>
       <c r="I60" t="n">
@@ -11429,7 +11429,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'K', 'wettability')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'K', 'wettability', 'volume_fraction')</t>
         </is>
       </c>
       <c r="I61" t="n">
@@ -11611,7 +11611,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'K', 'wettability', 'inclination')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'inclination', 'K', 'wettability')</t>
         </is>
       </c>
       <c r="I62" t="n">
@@ -11793,7 +11793,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'K', 'wettability', 'inclination')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'inclination', 'K', 'wettability')</t>
         </is>
       </c>
       <c r="I63" t="n">
@@ -11975,7 +11975,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'K', 'inclination')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'inclination', 'K', 'volume_fraction')</t>
         </is>
       </c>
       <c r="I64" t="n">
@@ -12157,7 +12157,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'K', 'inclination')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'inclination', 'K', 'volume_fraction')</t>
         </is>
       </c>
       <c r="I65" t="n">
@@ -12339,7 +12339,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'wettability', 'inclination')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'inclination', 'volume_fraction', 'wettability')</t>
         </is>
       </c>
       <c r="I66" t="n">
@@ -12521,7 +12521,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'wettability', 'inclination')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'inclination', 'volume_fraction', 'wettability')</t>
         </is>
       </c>
       <c r="I67" t="n">
@@ -12703,7 +12703,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'K', 'wettability', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'sedimentation_Stk', 'K', 'wettability')</t>
         </is>
       </c>
       <c r="I68" t="n">
@@ -12885,7 +12885,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'K', 'wettability', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'sedimentation_Stk', 'K', 'wettability')</t>
         </is>
       </c>
       <c r="I69" t="n">
@@ -13067,7 +13067,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'K', 'wettability', 'inclination', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'K', 'sedimentation_Stk', 'wettability')</t>
         </is>
       </c>
       <c r="I70" t="n">
@@ -13249,7 +13249,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'K', 'wettability', 'inclination', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'K', 'sedimentation_Stk', 'wettability')</t>
         </is>
       </c>
       <c r="I71" t="n">
@@ -13431,7 +13431,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'K', 'inclination', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'inclination', 'K', 'sedimentation_Stk')</t>
         </is>
       </c>
       <c r="I72" t="n">
@@ -13613,7 +13613,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'K', 'inclination', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'inclination', 'K', 'sedimentation_Stk')</t>
         </is>
       </c>
       <c r="I73" t="n">
@@ -13795,7 +13795,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'wettability', 'inclination', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'inclination', 'sedimentation_Stk', 'wettability')</t>
         </is>
       </c>
       <c r="I74" t="n">
@@ -13977,7 +13977,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'wettability', 'inclination', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'inclination', 'sedimentation_Stk', 'wettability')</t>
         </is>
       </c>
       <c r="I75" t="n">
@@ -14159,7 +14159,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'K', 'wettability', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'sedimentation_Stk', 'K', 'wettability')</t>
         </is>
       </c>
       <c r="I76" t="n">
@@ -14341,7 +14341,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'K', 'wettability', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'sedimentation_Stk', 'K', 'wettability')</t>
         </is>
       </c>
       <c r="I77" t="n">
@@ -14523,7 +14523,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'K', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'sedimentation_Stk', 'K', 'volume_fraction')</t>
         </is>
       </c>
       <c r="I78" t="n">
@@ -14705,7 +14705,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'K', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'sedimentation_Stk', 'K', 'volume_fraction')</t>
         </is>
       </c>
       <c r="I79" t="n">
@@ -14887,7 +14887,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'wettability', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'sedimentation_Stk', 'volume_fraction', 'wettability')</t>
         </is>
       </c>
       <c r="I80" t="n">
@@ -15069,7 +15069,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'wettability', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'sedimentation_Stk', 'volume_fraction', 'wettability')</t>
         </is>
       </c>
       <c r="I81" t="n">
@@ -15251,7 +15251,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'K', 'inclination', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'inclination', 'K', 'sedimentation_Stk')</t>
         </is>
       </c>
       <c r="I82" t="n">
@@ -15433,7 +15433,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'K', 'inclination', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'inclination', 'K', 'sedimentation_Stk')</t>
         </is>
       </c>
       <c r="I83" t="n">
@@ -15615,7 +15615,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'wettability', 'inclination', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'inclination', 'sedimentation_Stk', 'wettability')</t>
         </is>
       </c>
       <c r="I84" t="n">
@@ -15797,7 +15797,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'wettability', 'inclination', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'inclination', 'sedimentation_Stk', 'wettability')</t>
         </is>
       </c>
       <c r="I85" t="n">
@@ -15979,7 +15979,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'inclination', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'inclination', 'volume_fraction', 'sedimentation_Stk')</t>
         </is>
       </c>
       <c r="I86" t="n">
@@ -16161,7 +16161,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'inclination', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'inclination', 'volume_fraction', 'sedimentation_Stk')</t>
         </is>
       </c>
       <c r="I87" t="n">
@@ -16343,7 +16343,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'relative_roughness', 'wettability', 'K')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'relative_roughness', 'K', 'wettability')</t>
         </is>
       </c>
       <c r="I88" t="n">
@@ -16525,7 +16525,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'relative_roughness', 'wettability', 'K')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'relative_roughness', 'K', 'wettability')</t>
         </is>
       </c>
       <c r="I89" t="n">
@@ -16707,7 +16707,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'relative_roughness', 'wettability', 'inclination', 'K')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'K', 'wettability', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I90" t="n">
@@ -16889,7 +16889,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'relative_roughness', 'wettability', 'inclination', 'K')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'K', 'wettability', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I91" t="n">
@@ -17071,7 +17071,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'relative_roughness', 'inclination', 'K')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'inclination', 'K', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I92" t="n">
@@ -17253,7 +17253,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'relative_roughness', 'inclination', 'K')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'inclination', 'K', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I93" t="n">
@@ -17435,7 +17435,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'relative_roughness', 'wettability', 'inclination')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'inclination', 'relative_roughness', 'wettability')</t>
         </is>
       </c>
       <c r="I94" t="n">
@@ -17617,7 +17617,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'relative_roughness', 'wettability', 'inclination')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'inclination', 'relative_roughness', 'wettability')</t>
         </is>
       </c>
       <c r="I95" t="n">
@@ -17799,7 +17799,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'relative_roughness', 'wettability', 'K')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K', 'wettability')</t>
         </is>
       </c>
       <c r="I96" t="n">
@@ -17981,7 +17981,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'relative_roughness', 'wettability', 'K')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K', 'wettability')</t>
         </is>
       </c>
       <c r="I97" t="n">
@@ -18163,7 +18163,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'relative_roughness', 'K')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K', 'volume_fraction')</t>
         </is>
       </c>
       <c r="I98" t="n">
@@ -18345,7 +18345,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'relative_roughness', 'K')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K', 'volume_fraction')</t>
         </is>
       </c>
       <c r="I99" t="n">
@@ -18527,7 +18527,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'relative_roughness', 'wettability')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'relative_roughness', 'volume_fraction', 'wettability')</t>
         </is>
       </c>
       <c r="I100" t="n">
@@ -18709,7 +18709,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'relative_roughness', 'wettability')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'relative_roughness', 'volume_fraction', 'wettability')</t>
         </is>
       </c>
       <c r="I101" t="n">
@@ -18891,7 +18891,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'relative_roughness', 'inclination', 'K')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'inclination', 'K', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I102" t="n">
@@ -19073,7 +19073,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'relative_roughness', 'inclination', 'K')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'inclination', 'K', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I103" t="n">
@@ -19255,7 +19255,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'relative_roughness', 'wettability', 'inclination')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'inclination', 'relative_roughness', 'wettability')</t>
         </is>
       </c>
       <c r="I104" t="n">
@@ -19437,7 +19437,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'relative_roughness', 'wettability', 'inclination')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'inclination', 'relative_roughness', 'wettability')</t>
         </is>
       </c>
       <c r="I105" t="n">
@@ -19619,7 +19619,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'relative_roughness', 'inclination')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'inclination', 'volume_fraction', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I106" t="n">
@@ -19801,7 +19801,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'relative_roughness', 'inclination')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'inclination', 'volume_fraction', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I107" t="n">
@@ -19983,7 +19983,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'relative_roughness', 'wettability', 'K', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'sedimentation_Stk', 'K', 'wettability', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I108" t="n">
@@ -20165,7 +20165,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'relative_roughness', 'wettability', 'K', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'sedimentation_Stk', 'K', 'wettability', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I109" t="n">
@@ -20347,7 +20347,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'relative_roughness', 'K', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'sedimentation_Stk', 'K', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I110" t="n">
@@ -20529,7 +20529,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'relative_roughness', 'K', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'sedimentation_Stk', 'K', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I111" t="n">
@@ -20711,7 +20711,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'relative_roughness', 'wettability', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'sedimentation_Stk', 'relative_roughness', 'wettability')</t>
         </is>
       </c>
       <c r="I112" t="n">
@@ -20893,7 +20893,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'relative_roughness', 'wettability', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'sedimentation_Stk', 'relative_roughness', 'wettability')</t>
         </is>
       </c>
       <c r="I113" t="n">
@@ -21075,7 +21075,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'relative_roughness', 'inclination', 'K', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'K', 'sedimentation_Stk', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I114" t="n">
@@ -21257,7 +21257,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'relative_roughness', 'inclination', 'K', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'K', 'sedimentation_Stk', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I115" t="n">
@@ -21439,7 +21439,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'relative_roughness', 'wettability', 'inclination', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'relative_roughness', 'sedimentation_Stk', 'wettability')</t>
         </is>
       </c>
       <c r="I116" t="n">
@@ -21621,7 +21621,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'relative_roughness', 'wettability', 'inclination', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'relative_roughness', 'sedimentation_Stk', 'wettability')</t>
         </is>
       </c>
       <c r="I117" t="n">
@@ -21803,7 +21803,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'relative_roughness', 'inclination', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'inclination', 'relative_roughness', 'sedimentation_Stk')</t>
         </is>
       </c>
       <c r="I118" t="n">
@@ -21985,7 +21985,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'relative_roughness', 'inclination', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'inclination', 'relative_roughness', 'sedimentation_Stk')</t>
         </is>
       </c>
       <c r="I119" t="n">
@@ -22167,7 +22167,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'sedimentation_Stk', 'K', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I120" t="n">
@@ -22349,7 +22349,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'sedimentation_Stk', 'K', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I121" t="n">
@@ -22531,7 +22531,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'relative_roughness', 'wettability', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'sedimentation_Stk', 'relative_roughness', 'wettability')</t>
         </is>
       </c>
       <c r="I122" t="n">
@@ -22713,7 +22713,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'relative_roughness', 'wettability', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'sedimentation_Stk', 'relative_roughness', 'wettability')</t>
         </is>
       </c>
       <c r="I123" t="n">
@@ -22895,7 +22895,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'relative_roughness', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'sedimentation_Stk', 'volume_fraction', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I124" t="n">
@@ -23077,7 +23077,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'relative_roughness', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'sedimentation_Stk', 'volume_fraction', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I125" t="n">
@@ -23259,7 +23259,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'relative_roughness', 'inclination', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'inclination', 'relative_roughness', 'sedimentation_Stk')</t>
         </is>
       </c>
       <c r="I126" t="n">
@@ -23441,7 +23441,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'relative_roughness', 'inclination', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'inclination', 'relative_roughness', 'sedimentation_Stk')</t>
         </is>
       </c>
       <c r="I127" t="n">
@@ -23987,7 +23987,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'K', 'wettability', 'inclination')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'K', 'wettability')</t>
         </is>
       </c>
       <c r="I130" t="n">
@@ -24169,7 +24169,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'K', 'wettability', 'inclination')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'K', 'wettability')</t>
         </is>
       </c>
       <c r="I131" t="n">
@@ -24351,7 +24351,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'K', 'inclination')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'inclination', 'K')</t>
         </is>
       </c>
       <c r="I132" t="n">
@@ -24533,7 +24533,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'K', 'inclination')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'inclination', 'K')</t>
         </is>
       </c>
       <c r="I133" t="n">
@@ -24715,7 +24715,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'wettability', 'inclination')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'inclination', 'wettability')</t>
         </is>
       </c>
       <c r="I134" t="n">
@@ -24897,7 +24897,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'wettability', 'inclination')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'inclination', 'wettability')</t>
         </is>
       </c>
       <c r="I135" t="n">
@@ -25443,7 +25443,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'K')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'K', 'volume_fraction')</t>
         </is>
       </c>
       <c r="I138" t="n">
@@ -25625,7 +25625,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'K')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'K', 'volume_fraction')</t>
         </is>
       </c>
       <c r="I139" t="n">
@@ -26171,7 +26171,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'K', 'inclination')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'inclination', 'K')</t>
         </is>
       </c>
       <c r="I142" t="n">
@@ -26353,7 +26353,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'K', 'inclination')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'inclination', 'K')</t>
         </is>
       </c>
       <c r="I143" t="n">
@@ -26535,7 +26535,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'wettability', 'inclination')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'inclination', 'wettability')</t>
         </is>
       </c>
       <c r="I144" t="n">
@@ -26717,7 +26717,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'wettability', 'inclination')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'inclination', 'wettability')</t>
         </is>
       </c>
       <c r="I145" t="n">
@@ -26899,7 +26899,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'inclination')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'inclination', 'volume_fraction')</t>
         </is>
       </c>
       <c r="I146" t="n">
@@ -27081,7 +27081,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'inclination')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'inclination', 'volume_fraction')</t>
         </is>
       </c>
       <c r="I147" t="n">
@@ -27263,7 +27263,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'K', 'wettability', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'sedimentation_Stk', 'K', 'wettability')</t>
         </is>
       </c>
       <c r="I148" t="n">
@@ -27445,7 +27445,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'K', 'wettability', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'sedimentation_Stk', 'K', 'wettability')</t>
         </is>
       </c>
       <c r="I149" t="n">
@@ -27627,7 +27627,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'K', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'sedimentation_Stk', 'K')</t>
         </is>
       </c>
       <c r="I150" t="n">
@@ -27809,7 +27809,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'K', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'sedimentation_Stk', 'K')</t>
         </is>
       </c>
       <c r="I151" t="n">
@@ -27991,7 +27991,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'wettability', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'sedimentation_Stk', 'wettability')</t>
         </is>
       </c>
       <c r="I152" t="n">
@@ -28173,7 +28173,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'wettability', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'sedimentation_Stk', 'wettability')</t>
         </is>
       </c>
       <c r="I153" t="n">
@@ -28355,7 +28355,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'K', 'inclination', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'K', 'sedimentation_Stk')</t>
         </is>
       </c>
       <c r="I154" t="n">
@@ -28537,7 +28537,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'K', 'inclination', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'K', 'sedimentation_Stk')</t>
         </is>
       </c>
       <c r="I155" t="n">
@@ -28719,7 +28719,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'wettability', 'inclination', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'sedimentation_Stk', 'wettability')</t>
         </is>
       </c>
       <c r="I156" t="n">
@@ -28901,7 +28901,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'wettability', 'inclination', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'sedimentation_Stk', 'wettability')</t>
         </is>
       </c>
       <c r="I157" t="n">
@@ -29447,7 +29447,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'K', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'sedimentation_Stk', 'K')</t>
         </is>
       </c>
       <c r="I160" t="n">
@@ -29629,7 +29629,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'K', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'sedimentation_Stk', 'K')</t>
         </is>
       </c>
       <c r="I161" t="n">
@@ -29811,7 +29811,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'wettability', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'sedimentation_Stk', 'wettability')</t>
         </is>
       </c>
       <c r="I162" t="n">
@@ -29993,7 +29993,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'wettability', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'sedimentation_Stk', 'wettability')</t>
         </is>
       </c>
       <c r="I163" t="n">
@@ -30175,7 +30175,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'sedimentation_Stk', 'volume_fraction')</t>
         </is>
       </c>
       <c r="I164" t="n">
@@ -30357,7 +30357,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'sedimentation_Stk', 'volume_fraction')</t>
         </is>
       </c>
       <c r="I165" t="n">
@@ -30903,7 +30903,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'relative_roughness', 'wettability', 'K')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'relative_roughness', 'K', 'wettability')</t>
         </is>
       </c>
       <c r="I168" t="n">
@@ -31085,7 +31085,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'relative_roughness', 'wettability', 'K')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'relative_roughness', 'K', 'wettability')</t>
         </is>
       </c>
       <c r="I169" t="n">
@@ -31995,7 +31995,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'relative_roughness', 'inclination', 'K')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'K', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I174" t="n">
@@ -32177,7 +32177,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'relative_roughness', 'inclination', 'K')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'K', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I175" t="n">
@@ -32359,7 +32359,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'relative_roughness', 'wettability', 'inclination')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'relative_roughness', 'wettability')</t>
         </is>
       </c>
       <c r="I176" t="n">
@@ -32541,7 +32541,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'relative_roughness', 'wettability', 'inclination')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'relative_roughness', 'wettability')</t>
         </is>
       </c>
       <c r="I177" t="n">
@@ -32723,7 +32723,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'relative_roughness', 'inclination')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'inclination', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I178" t="n">
@@ -32905,7 +32905,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'relative_roughness', 'inclination')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'inclination', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I179" t="n">
@@ -33815,7 +33815,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'relative_roughness')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'relative_roughness', 'volume_fraction')</t>
         </is>
       </c>
       <c r="I184" t="n">
@@ -33997,7 +33997,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'volume_fraction', 'relative_roughness')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'relative_roughness', 'volume_fraction')</t>
         </is>
       </c>
       <c r="I185" t="n">
@@ -34179,7 +34179,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'relative_roughness', 'inclination')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'inclination', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I186" t="n">
@@ -34361,7 +34361,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'relative_roughness', 'inclination')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'inclination', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I187" t="n">
@@ -34543,7 +34543,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'relative_roughness', 'K', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'sedimentation_Stk', 'K', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I188" t="n">
@@ -34725,7 +34725,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'relative_roughness', 'K', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'sedimentation_Stk', 'K', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I189" t="n">
@@ -34907,7 +34907,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'relative_roughness', 'wettability', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'sedimentation_Stk', 'relative_roughness', 'wettability')</t>
         </is>
       </c>
       <c r="I190" t="n">
@@ -35089,7 +35089,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'relative_roughness', 'wettability', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'sedimentation_Stk', 'relative_roughness', 'wettability')</t>
         </is>
       </c>
       <c r="I191" t="n">
@@ -35271,7 +35271,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'relative_roughness', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'sedimentation_Stk', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I192" t="n">
@@ -35453,7 +35453,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'relative_roughness', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'volume_fraction', 'sedimentation_Stk', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I193" t="n">
@@ -35635,7 +35635,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'relative_roughness', 'inclination', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'relative_roughness', 'sedimentation_Stk')</t>
         </is>
       </c>
       <c r="I194" t="n">
@@ -35817,7 +35817,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'relative_roughness', 'inclination', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'relative_roughness', 'sedimentation_Stk')</t>
         </is>
       </c>
       <c r="I195" t="n">
@@ -35999,7 +35999,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'relative_roughness', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'sedimentation_Stk', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I196" t="n">
@@ -36181,7 +36181,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'relative_roughness', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'particle_droplet_diameter_ratio', 'sedimentation_Stk', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I197" t="n">
@@ -37455,7 +37455,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'K', 'inclination')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'K')</t>
         </is>
       </c>
       <c r="I204" t="n">
@@ -37637,7 +37637,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'K', 'inclination')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'K')</t>
         </is>
       </c>
       <c r="I205" t="n">
@@ -37819,7 +37819,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'wettability', 'inclination')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'wettability')</t>
         </is>
       </c>
       <c r="I206" t="n">
@@ -38001,7 +38001,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'wettability', 'inclination')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'wettability')</t>
         </is>
       </c>
       <c r="I207" t="n">
@@ -40003,7 +40003,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'K', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'sedimentation_Stk', 'K')</t>
         </is>
       </c>
       <c r="I218" t="n">
@@ -40185,7 +40185,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'K', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'sedimentation_Stk', 'K')</t>
         </is>
       </c>
       <c r="I219" t="n">
@@ -40367,7 +40367,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'wettability', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'sedimentation_Stk', 'wettability')</t>
         </is>
       </c>
       <c r="I220" t="n">
@@ -40549,7 +40549,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'wettability', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'sedimentation_Stk', 'wettability')</t>
         </is>
       </c>
       <c r="I221" t="n">
@@ -42915,7 +42915,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'relative_roughness', 'inclination')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I234" t="n">
@@ -43097,7 +43097,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'relative_roughness', 'inclination')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'inclination', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I235" t="n">
@@ -43643,7 +43643,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'relative_roughness', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'sedimentation_Stk', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I238" t="n">
@@ -43825,7 +43825,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'relative_roughness', 'sedimentation_Stk')</t>
+          <t>('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re', 'sedimentation_Stk', 'relative_roughness')</t>
         </is>
       </c>
       <c r="I239" t="n">
